--- a/docs/app/api/files/results-4.xlsx
+++ b/docs/app/api/files/results-4.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: March · solver HiGHS Optimal · run 2026-09-04 09:46 UTC · 31 ms</t>
+          <t>Conditions: March · solver HiGHS Optimal · run 2026-09-28 18:35 UTC · 66 ms</t>
         </is>
       </c>
     </row>
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13319044.75</v>
+        <v>13319199.62</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -563,11 +563,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-1950104.14</v>
+        <v>2075021.14</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>worse</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>777.28</v>
+        <v>777.2</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -586,11 +586,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-236.39</v>
+        <v>121.08</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>worse</t>
         </is>
       </c>
     </row>
@@ -609,11 +609,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.83</v>
+        <v>0.42</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>worse</t>
         </is>
       </c>
     </row>
@@ -632,11 +632,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.1209</v>
+        <v>0</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>flat</t>
         </is>
       </c>
     </row>
@@ -655,11 +655,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.1209</v>
+        <v>0</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>flat</t>
         </is>
       </c>
     </row>
@@ -678,11 +678,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.3369</v>
+        <v>0</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>flat</t>
         </is>
       </c>
     </row>
@@ -701,11 +701,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.3369</v>
+        <v>0</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>flat</t>
         </is>
       </c>
     </row>
@@ -724,11 +724,11 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.1209</v>
+        <v>0.0076</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>worse</t>
         </is>
       </c>
     </row>
@@ -747,11 +747,11 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-24</v>
+        <v>5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>worse</t>
         </is>
       </c>
     </row>
@@ -770,11 +770,11 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-19</v>
+        <v>0</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>flat</t>
         </is>
       </c>
     </row>
@@ -940,23 +940,23 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Port Province</t>
+          <t>National Capital District</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>168000</v>
       </c>
       <c r="E2" t="n">
-        <v>587.554</v>
+        <v>588.05</v>
       </c>
       <c r="F2" t="n">
-        <v>587.554</v>
+        <v>588.05</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>214423.7</v>
+        <v>214579.72</v>
       </c>
       <c r="I2" t="n">
         <v>1.28</v>
@@ -980,7 +980,7 @@
         <v>0.08</v>
       </c>
       <c r="N2" t="n">
-        <v>108.1</v>
+        <v>108</v>
       </c>
       <c r="O2" t="n">
         <v>0.0262</v>
@@ -1024,7 +1024,7 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>170648.47</v>
+        <v>170630.63</v>
       </c>
       <c r="I3" t="n">
         <v>1.29</v>
@@ -1092,7 +1092,7 @@
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>77640.17999999999</v>
+        <v>77631.94</v>
       </c>
       <c r="I4" t="n">
         <v>1.27</v>
@@ -1160,7 +1160,7 @@
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>69070.03</v>
+        <v>69062.73</v>
       </c>
       <c r="I5" t="n">
         <v>1.28</v>
@@ -1228,7 +1228,7 @@
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>48978.86</v>
+        <v>48973.73</v>
       </c>
       <c r="I6" t="n">
         <v>1.29</v>
@@ -1296,7 +1296,7 @@
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>70937.42</v>
+        <v>70931.07000000001</v>
       </c>
       <c r="I7" t="n">
         <v>1.51</v>
@@ -1364,7 +1364,7 @@
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>552459.51</v>
+        <v>552453.83</v>
       </c>
       <c r="I8" t="n">
         <v>13.15</v>
@@ -1432,7 +1432,7 @@
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>35793.97</v>
+        <v>35791.4</v>
       </c>
       <c r="I9" t="n">
         <v>1.88</v>
@@ -1500,7 +1500,7 @@
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>63956.46</v>
+        <v>63951.32</v>
       </c>
       <c r="I10" t="n">
         <v>1.68</v>
@@ -1568,7 +1568,7 @@
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>142934.3</v>
+        <v>142932.67</v>
       </c>
       <c r="I11" t="n">
         <v>11.91</v>
@@ -1636,7 +1636,7 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>210460.76</v>
+        <v>210458.6</v>
       </c>
       <c r="I12" t="n">
         <v>13.15</v>
@@ -1704,7 +1704,7 @@
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>116106.32</v>
+        <v>116098.48</v>
       </c>
       <c r="I13" t="n">
         <v>2</v>
@@ -1772,7 +1772,7 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>36201.91</v>
+        <v>36199.08</v>
       </c>
       <c r="I14" t="n">
         <v>1.72</v>
@@ -1840,7 +1840,7 @@
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>55164.82</v>
+        <v>55160.5</v>
       </c>
       <c r="I15" t="n">
         <v>1.72</v>
@@ -1908,7 +1908,7 @@
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>31030.21</v>
+        <v>31027.78</v>
       </c>
       <c r="I16" t="n">
         <v>1.72</v>
@@ -1976,7 +1976,7 @@
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>315691.15</v>
+        <v>315687.9</v>
       </c>
       <c r="I17" t="n">
         <v>13.15</v>
@@ -2044,7 +2044,7 @@
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>138531.25</v>
+        <v>138529.76</v>
       </c>
       <c r="I18" t="n">
         <v>12.59</v>
@@ -2112,7 +2112,7 @@
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>78916.34</v>
+        <v>78910.39</v>
       </c>
       <c r="I19" t="n">
         <v>1.79</v>
@@ -2180,7 +2180,7 @@
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>66390.53</v>
+        <v>66385.25999999999</v>
       </c>
       <c r="I20" t="n">
         <v>1.7</v>
@@ -2248,7 +2248,7 @@
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>47665</v>
+        <v>47661.21</v>
       </c>
       <c r="I21" t="n">
         <v>1.7</v>
@@ -2316,7 +2316,7 @@
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>52771.96</v>
+        <v>52767.77</v>
       </c>
       <c r="I22" t="n">
         <v>1.7</v>
@@ -2384,7 +2384,7 @@
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>102790.34</v>
+        <v>102789.13</v>
       </c>
       <c r="I23" t="n">
         <v>11.42</v>
@@ -2452,7 +2452,7 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>97079.77</v>
+        <v>97078.62</v>
       </c>
       <c r="I24" t="n">
         <v>11.42</v>
@@ -2520,7 +2520,7 @@
         <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>12767.41</v>
+        <v>12766.4</v>
       </c>
       <c r="I25" t="n">
         <v>1.7</v>
@@ -2588,7 +2588,7 @@
         <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>105046.08</v>
+        <v>105037.7</v>
       </c>
       <c r="I26" t="n">
         <v>1.69</v>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Losuia Province</t>
+          <t>Milne Bay</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -2656,7 +2656,7 @@
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>97489.75</v>
+        <v>97485.83</v>
       </c>
       <c r="I27" t="n">
         <v>3.36</v>
@@ -2724,7 +2724,7 @@
         <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>70596.03</v>
+        <v>70593.19</v>
       </c>
       <c r="I28" t="n">
         <v>3.36</v>
@@ -2792,7 +2792,7 @@
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>80681.17</v>
+        <v>80677.92999999999</v>
       </c>
       <c r="I29" t="n">
         <v>3.36</v>
@@ -2860,7 +2860,7 @@
         <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>47064.02</v>
+        <v>47062.13</v>
       </c>
       <c r="I30" t="n">
         <v>3.36</v>
@@ -2928,7 +2928,7 @@
         <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>28802.96</v>
+        <v>28800.66</v>
       </c>
       <c r="I31" t="n">
         <v>1.69</v>
@@ -2996,7 +2996,7 @@
         <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>50425.73</v>
+        <v>50423.71</v>
       </c>
       <c r="I32" t="n">
         <v>3.36</v>
@@ -3064,7 +3064,7 @@
         <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>134881.6</v>
+        <v>134872</v>
       </c>
       <c r="I33" t="n">
         <v>1.9</v>
@@ -3132,7 +3132,7 @@
         <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>41794.3</v>
+        <v>41791.32</v>
       </c>
       <c r="I34" t="n">
         <v>1.9</v>
@@ -3200,7 +3200,7 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>24696.63</v>
+        <v>24694.87</v>
       </c>
       <c r="I35" t="n">
         <v>1.9</v>
@@ -3268,7 +3268,7 @@
         <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>123233.68</v>
+        <v>123232.33</v>
       </c>
       <c r="I36" t="n">
         <v>12.32</v>
@@ -3336,7 +3336,7 @@
         <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>20897.15</v>
+        <v>20895.66</v>
       </c>
       <c r="I37" t="n">
         <v>1.9</v>
@@ -3404,7 +3404,7 @@
         <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>26596.37</v>
+        <v>26594.48</v>
       </c>
       <c r="I38" t="n">
         <v>1.9</v>
@@ -3456,26 +3456,26 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Angau Province</t>
+          <t>Morobe</t>
         </is>
       </c>
       <c r="D39" t="n">
         <v>188000</v>
       </c>
       <c r="E39" t="n">
-        <v>656.3200000000001</v>
+        <v>658.056</v>
       </c>
       <c r="F39" t="n">
-        <v>656.3200000000001</v>
+        <v>658.056</v>
       </c>
       <c r="G39" t="n">
         <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>273144.96</v>
+        <v>273834.02</v>
       </c>
       <c r="I39" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>0.08</v>
       </c>
       <c r="N39" t="n">
-        <v>108.3</v>
+        <v>108</v>
       </c>
       <c r="O39" t="n">
         <v>0.0252</v>
@@ -3540,7 +3540,7 @@
         <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>90699.39999999999</v>
+        <v>90692.10000000001</v>
       </c>
       <c r="I40" t="n">
         <v>1.68</v>
@@ -3608,7 +3608,7 @@
         <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>56767.35</v>
+        <v>56763.16</v>
       </c>
       <c r="I41" t="n">
         <v>1.83</v>
@@ -3676,7 +3676,7 @@
         <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>77837.23</v>
+        <v>77831.55</v>
       </c>
       <c r="I42" t="n">
         <v>1.85</v>
@@ -3744,7 +3744,7 @@
         <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>73574.3</v>
+        <v>73569.42999999999</v>
       </c>
       <c r="I43" t="n">
         <v>2.04</v>
@@ -3812,7 +3812,7 @@
         <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>225498.25</v>
+        <v>225495.69</v>
       </c>
       <c r="I44" t="n">
         <v>11.87</v>
@@ -3880,7 +3880,7 @@
         <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>31505.54</v>
+        <v>31503.25</v>
       </c>
       <c r="I45" t="n">
         <v>1.85</v>
@@ -3948,7 +3948,7 @@
         <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>38104.82</v>
+        <v>38101.71</v>
       </c>
       <c r="I46" t="n">
         <v>1.66</v>
@@ -4000,7 +4000,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Modilon Province</t>
+          <t>Madang</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -4016,7 +4016,7 @@
         <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>150792.9</v>
+        <v>150779.93</v>
       </c>
       <c r="I47" t="n">
         <v>1.57</v>
@@ -4084,7 +4084,7 @@
         <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>551530.64</v>
+        <v>551525.1</v>
       </c>
       <c r="I48" t="n">
         <v>13.45</v>
@@ -4152,7 +4152,7 @@
         <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>56333.89</v>
+        <v>56330.38</v>
       </c>
       <c r="I49" t="n">
         <v>2.17</v>
@@ -4220,7 +4220,7 @@
         <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>47016.39</v>
+        <v>47013.42</v>
       </c>
       <c r="I50" t="n">
         <v>2.14</v>
@@ -4288,7 +4288,7 @@
         <v>1</v>
       </c>
       <c r="H51" t="n">
-        <v>376655.07</v>
+        <v>376651.29</v>
       </c>
       <c r="I51" t="n">
         <v>13.45</v>
@@ -4356,7 +4356,7 @@
         <v>1</v>
       </c>
       <c r="H52" t="n">
-        <v>131391.03</v>
+        <v>131389.41</v>
       </c>
       <c r="I52" t="n">
         <v>10.95</v>
@@ -4424,7 +4424,7 @@
         <v>1</v>
       </c>
       <c r="H53" t="n">
-        <v>177301.59</v>
+        <v>177299.7</v>
       </c>
       <c r="I53" t="n">
         <v>12.66</v>
@@ -4492,7 +4492,7 @@
         <v>1</v>
       </c>
       <c r="H54" t="n">
-        <v>180683.26</v>
+        <v>180671.37</v>
       </c>
       <c r="I54" t="n">
         <v>2.05</v>
@@ -4560,7 +4560,7 @@
         <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>106767.38</v>
+        <v>106760.35</v>
       </c>
       <c r="I55" t="n">
         <v>2.05</v>
@@ -4628,7 +4628,7 @@
         <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>90341.63</v>
+        <v>90335.67999999999</v>
       </c>
       <c r="I56" t="n">
         <v>2.05</v>
@@ -4696,7 +4696,7 @@
         <v>1</v>
       </c>
       <c r="H57" t="n">
-        <v>61431.92</v>
+        <v>61428.67</v>
       </c>
       <c r="I57" t="n">
         <v>2.56</v>
@@ -4764,7 +4764,7 @@
         <v>1</v>
       </c>
       <c r="H58" t="n">
-        <v>67756.22</v>
+        <v>67751.75999999999</v>
       </c>
       <c r="I58" t="n">
         <v>2.05</v>
@@ -4832,7 +4832,7 @@
         <v>1</v>
       </c>
       <c r="H59" t="n">
-        <v>55436.91</v>
+        <v>55433.26</v>
       </c>
       <c r="I59" t="n">
         <v>2.05</v>
@@ -4900,7 +4900,7 @@
         <v>1</v>
       </c>
       <c r="H60" t="n">
-        <v>38394.95</v>
+        <v>38392.92</v>
       </c>
       <c r="I60" t="n">
         <v>2.56</v>
@@ -4968,7 +4968,7 @@
         <v>1</v>
       </c>
       <c r="H61" t="n">
-        <v>96501.28999999999</v>
+        <v>96494.92999999999</v>
       </c>
       <c r="I61" t="n">
         <v>2.05</v>
@@ -5036,7 +5036,7 @@
         <v>1</v>
       </c>
       <c r="H62" t="n">
-        <v>80075.53999999999</v>
+        <v>80070.25999999999</v>
       </c>
       <c r="I62" t="n">
         <v>2.05</v>
@@ -5104,7 +5104,7 @@
         <v>1</v>
       </c>
       <c r="H63" t="n">
-        <v>49277.25</v>
+        <v>49274.01</v>
       </c>
       <c r="I63" t="n">
         <v>2.05</v>
@@ -5172,7 +5172,7 @@
         <v>1</v>
       </c>
       <c r="H64" t="n">
-        <v>45170.82</v>
+        <v>45167.84</v>
       </c>
       <c r="I64" t="n">
         <v>2.05</v>
@@ -5240,7 +5240,7 @@
         <v>1</v>
       </c>
       <c r="H65" t="n">
-        <v>256626.64</v>
+        <v>256624.21</v>
       </c>
       <c r="I65" t="n">
         <v>14.26</v>
@@ -5308,7 +5308,7 @@
         <v>1</v>
       </c>
       <c r="H66" t="n">
-        <v>159859.28</v>
+        <v>159857.52</v>
       </c>
       <c r="I66" t="n">
         <v>12.3</v>
@@ -5376,7 +5376,7 @@
         <v>1</v>
       </c>
       <c r="H67" t="n">
-        <v>156827.39</v>
+        <v>156825.91</v>
       </c>
       <c r="I67" t="n">
         <v>14.26</v>
@@ -5444,7 +5444,7 @@
         <v>1</v>
       </c>
       <c r="H68" t="n">
-        <v>131621.47</v>
+        <v>131611.6</v>
       </c>
       <c r="I68" t="n">
         <v>1.83</v>
@@ -5512,7 +5512,7 @@
         <v>1</v>
       </c>
       <c r="H69" t="n">
-        <v>83916.84</v>
+        <v>83910.25999999999</v>
       </c>
       <c r="I69" t="n">
         <v>1.75</v>
@@ -5580,7 +5580,7 @@
         <v>1</v>
       </c>
       <c r="H70" t="n">
-        <v>78260.56</v>
+        <v>78255.35000000001</v>
       </c>
       <c r="I70" t="n">
         <v>2.06</v>
@@ -5648,7 +5648,7 @@
         <v>1</v>
       </c>
       <c r="H71" t="n">
-        <v>91052.99000000001</v>
+        <v>91047.37</v>
       </c>
       <c r="I71" t="n">
         <v>2.22</v>
@@ -5716,7 +5716,7 @@
         <v>1</v>
       </c>
       <c r="H72" t="n">
-        <v>55754.43</v>
+        <v>55750.45</v>
       </c>
       <c r="I72" t="n">
         <v>1.92</v>
@@ -5784,7 +5784,7 @@
         <v>1</v>
       </c>
       <c r="H73" t="n">
-        <v>63671.59</v>
+        <v>63667.2</v>
       </c>
       <c r="I73" t="n">
         <v>1.99</v>
@@ -5852,7 +5852,7 @@
         <v>1</v>
       </c>
       <c r="H74" t="n">
-        <v>191644.7</v>
+        <v>191633.18</v>
       </c>
       <c r="I74" t="n">
         <v>2.28</v>
@@ -5920,7 +5920,7 @@
         <v>1</v>
       </c>
       <c r="H75" t="n">
-        <v>103111.82</v>
+        <v>103105.92</v>
       </c>
       <c r="I75" t="n">
         <v>2.4</v>
@@ -5988,7 +5988,7 @@
         <v>1</v>
       </c>
       <c r="H76" t="n">
-        <v>72512.25999999999</v>
+        <v>72508</v>
       </c>
       <c r="I76" t="n">
         <v>2.34</v>
@@ -6056,7 +6056,7 @@
         <v>1</v>
       </c>
       <c r="H77" t="n">
-        <v>58241.49</v>
+        <v>58237.79</v>
       </c>
       <c r="I77" t="n">
         <v>2.16</v>
@@ -6124,7 +6124,7 @@
         <v>1</v>
       </c>
       <c r="H78" t="n">
-        <v>213826.87</v>
+        <v>213824.67</v>
       </c>
       <c r="I78" t="n">
         <v>13.36</v>
@@ -6192,7 +6192,7 @@
         <v>1</v>
       </c>
       <c r="H79" t="n">
-        <v>145043.35</v>
+        <v>145032.52</v>
       </c>
       <c r="I79" t="n">
         <v>1.84</v>
@@ -6260,7 +6260,7 @@
         <v>1</v>
       </c>
       <c r="H80" t="n">
-        <v>78348.92999999999</v>
+        <v>78342.89</v>
       </c>
       <c r="I80" t="n">
         <v>1.78</v>
@@ -6328,7 +6328,7 @@
         <v>1</v>
       </c>
       <c r="H81" t="n">
-        <v>70506.22</v>
+        <v>70501.28999999999</v>
       </c>
       <c r="I81" t="n">
         <v>1.96</v>
@@ -6396,7 +6396,7 @@
         <v>1</v>
       </c>
       <c r="H82" t="n">
-        <v>80482.92999999999</v>
+        <v>80477.59</v>
       </c>
       <c r="I82" t="n">
         <v>2.06</v>
@@ -6464,7 +6464,7 @@
         <v>1</v>
       </c>
       <c r="H83" t="n">
-        <v>46989.5</v>
+        <v>46986.34</v>
       </c>
       <c r="I83" t="n">
         <v>2.04</v>
@@ -6532,7 +6532,7 @@
         <v>1</v>
       </c>
       <c r="H84" t="n">
-        <v>52640.82</v>
+        <v>52636.99</v>
       </c>
       <c r="I84" t="n">
         <v>1.88</v>
@@ -6600,7 +6600,7 @@
         <v>1</v>
       </c>
       <c r="H85" t="n">
-        <v>178045.64</v>
+        <v>178030.28</v>
       </c>
       <c r="I85" t="n">
         <v>1.59</v>
@@ -6668,7 +6668,7 @@
         <v>1</v>
       </c>
       <c r="H86" t="n">
-        <v>60095.06</v>
+        <v>60090.4</v>
       </c>
       <c r="I86" t="n">
         <v>1.77</v>
@@ -6736,7 +6736,7 @@
         <v>1</v>
       </c>
       <c r="H87" t="n">
-        <v>55413.53</v>
+        <v>55409.28</v>
       </c>
       <c r="I87" t="n">
         <v>1.79</v>
@@ -6804,7 +6804,7 @@
         <v>1</v>
       </c>
       <c r="H88" t="n">
-        <v>37647.24</v>
+        <v>37644.22</v>
       </c>
       <c r="I88" t="n">
         <v>1.71</v>
@@ -6872,7 +6872,7 @@
         <v>1</v>
       </c>
       <c r="H89" t="n">
-        <v>42886.28</v>
+        <v>42882.72</v>
       </c>
       <c r="I89" t="n">
         <v>1.65</v>
@@ -6940,7 +6940,7 @@
         <v>1</v>
       </c>
       <c r="H90" t="n">
-        <v>101613.55</v>
+        <v>101605.59</v>
       </c>
       <c r="I90" t="n">
         <v>1.75</v>
@@ -7008,7 +7008,7 @@
         <v>1</v>
       </c>
       <c r="H91" t="n">
-        <v>71102.77</v>
+        <v>71097.14999999999</v>
       </c>
       <c r="I91" t="n">
         <v>1.73</v>
@@ -7076,7 +7076,7 @@
         <v>1</v>
       </c>
       <c r="H92" t="n">
-        <v>80875.39999999999</v>
+        <v>80868.96000000001</v>
       </c>
       <c r="I92" t="n">
         <v>1.72</v>
@@ -7144,7 +7144,7 @@
         <v>1</v>
       </c>
       <c r="H93" t="n">
-        <v>45118.79</v>
+        <v>45115.5</v>
       </c>
       <c r="I93" t="n">
         <v>1.88</v>
@@ -7212,7 +7212,7 @@
         <v>1</v>
       </c>
       <c r="H94" t="n">
-        <v>219336.44</v>
+        <v>219333.83</v>
       </c>
       <c r="I94" t="n">
         <v>11.54</v>
@@ -7280,7 +7280,7 @@
         <v>1</v>
       </c>
       <c r="H95" t="n">
-        <v>138345.15</v>
+        <v>138335</v>
       </c>
       <c r="I95" t="n">
         <v>1.87</v>
@@ -7348,7 +7348,7 @@
         <v>1</v>
       </c>
       <c r="H96" t="n">
-        <v>83105.53</v>
+        <v>83099.23</v>
       </c>
       <c r="I96" t="n">
         <v>1.81</v>
@@ -7416,7 +7416,7 @@
         <v>1</v>
       </c>
       <c r="H97" t="n">
-        <v>65311.06</v>
+        <v>65306.53</v>
       </c>
       <c r="I97" t="n">
         <v>1.98</v>
@@ -7484,7 +7484,7 @@
         <v>1</v>
       </c>
       <c r="H98" t="n">
-        <v>247202.4</v>
+        <v>247199.52</v>
       </c>
       <c r="I98" t="n">
         <v>11.77</v>
@@ -7552,7 +7552,7 @@
         <v>1</v>
       </c>
       <c r="H99" t="n">
-        <v>56104.94</v>
+        <v>56100.96</v>
       </c>
       <c r="I99" t="n">
         <v>1.93</v>
@@ -7620,7 +7620,7 @@
         <v>1</v>
       </c>
       <c r="H100" t="n">
-        <v>50642.59</v>
+        <v>50639.16</v>
       </c>
       <c r="I100" t="n">
         <v>2.03</v>
@@ -7667,28 +7667,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Goroka Base Hospital</t>
+          <t>Goroka Provincial Hospital</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Goroka Province</t>
+          <t>Eastern Highlands</t>
         </is>
       </c>
       <c r="D101" t="n">
         <v>108000</v>
       </c>
       <c r="E101" t="n">
-        <v>378.156</v>
+        <v>378.032</v>
       </c>
       <c r="F101" t="n">
-        <v>378.156</v>
+        <v>378.032</v>
       </c>
       <c r="G101" t="n">
         <v>1</v>
       </c>
       <c r="H101" t="n">
-        <v>227204.26</v>
+        <v>227115.73</v>
       </c>
       <c r="I101" t="n">
         <v>2.1</v>
@@ -7756,7 +7756,7 @@
         <v>1</v>
       </c>
       <c r="H102" t="n">
-        <v>118383.25</v>
+        <v>118374.87</v>
       </c>
       <c r="I102" t="n">
         <v>1.91</v>
@@ -7824,7 +7824,7 @@
         <v>1</v>
       </c>
       <c r="H103" t="n">
-        <v>76066.91</v>
+        <v>76062.32000000001</v>
       </c>
       <c r="I103" t="n">
         <v>2.24</v>
@@ -7892,7 +7892,7 @@
         <v>1</v>
       </c>
       <c r="H104" t="n">
-        <v>75361.2</v>
+        <v>75357.00999999999</v>
       </c>
       <c r="I104" t="n">
         <v>2.43</v>
@@ -7960,7 +7960,7 @@
         <v>1</v>
       </c>
       <c r="H105" t="n">
-        <v>63013.54</v>
+        <v>63009.75</v>
       </c>
       <c r="I105" t="n">
         <v>2.25</v>
@@ -8028,7 +8028,7 @@
         <v>1</v>
       </c>
       <c r="H106" t="n">
-        <v>160203.79</v>
+        <v>160202.03</v>
       </c>
       <c r="I106" t="n">
         <v>12.32</v>
@@ -8096,7 +8096,7 @@
         <v>1</v>
       </c>
       <c r="H107" t="n">
-        <v>135557.05</v>
+        <v>135555.56</v>
       </c>
       <c r="I107" t="n">
         <v>12.32</v>
@@ -8164,7 +8164,7 @@
         <v>1</v>
       </c>
       <c r="H108" t="n">
-        <v>90857.35000000001</v>
+        <v>90852.75</v>
       </c>
       <c r="I108" t="n">
         <v>2.67</v>
@@ -8232,7 +8232,7 @@
         <v>1</v>
       </c>
       <c r="H109" t="n">
-        <v>24050.47</v>
+        <v>24049.26</v>
       </c>
       <c r="I109" t="n">
         <v>2.67</v>
@@ -8300,7 +8300,7 @@
         <v>1</v>
       </c>
       <c r="H110" t="n">
-        <v>17369.79</v>
+        <v>17368.91</v>
       </c>
       <c r="I110" t="n">
         <v>2.67</v>
@@ -8368,7 +8368,7 @@
         <v>1</v>
       </c>
       <c r="H111" t="n">
-        <v>14697.51</v>
+        <v>14696.77</v>
       </c>
       <c r="I111" t="n">
         <v>2.67</v>
@@ -8436,7 +8436,7 @@
         <v>1</v>
       </c>
       <c r="H112" t="n">
-        <v>13361.37</v>
+        <v>13360.7</v>
       </c>
       <c r="I112" t="n">
         <v>2.67</v>
@@ -8488,7 +8488,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Kavieng Province</t>
+          <t>New Ireland</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -8504,7 +8504,7 @@
         <v>1</v>
       </c>
       <c r="H113" t="n">
-        <v>128809.37</v>
+        <v>128801.53</v>
       </c>
       <c r="I113" t="n">
         <v>2.22</v>
@@ -8572,7 +8572,7 @@
         <v>1</v>
       </c>
       <c r="H114" t="n">
-        <v>102159.16</v>
+        <v>102152.94</v>
       </c>
       <c r="I114" t="n">
         <v>2.22</v>
@@ -8640,7 +8640,7 @@
         <v>1</v>
       </c>
       <c r="H115" t="n">
-        <v>42732.01</v>
+        <v>42729.44</v>
       </c>
       <c r="I115" t="n">
         <v>2.25</v>
@@ -8708,7 +8708,7 @@
         <v>1</v>
       </c>
       <c r="H116" t="n">
-        <v>37754.47</v>
+        <v>37752.17</v>
       </c>
       <c r="I116" t="n">
         <v>2.22</v>
@@ -8776,7 +8776,7 @@
         <v>1</v>
       </c>
       <c r="H117" t="n">
-        <v>17992.43</v>
+        <v>17991.34</v>
       </c>
       <c r="I117" t="n">
         <v>2.25</v>
@@ -8844,7 +8844,7 @@
         <v>1</v>
       </c>
       <c r="H118" t="n">
-        <v>31486.74</v>
+        <v>31484.85</v>
       </c>
       <c r="I118" t="n">
         <v>2.25</v>
@@ -8912,7 +8912,7 @@
         <v>1</v>
       </c>
       <c r="H119" t="n">
-        <v>162375.59</v>
+        <v>162363.15</v>
       </c>
       <c r="I119" t="n">
         <v>1.76</v>
@@ -8980,7 +8980,7 @@
         <v>1</v>
       </c>
       <c r="H120" t="n">
-        <v>102684.96</v>
+        <v>102676.72</v>
       </c>
       <c r="I120" t="n">
         <v>1.68</v>
@@ -9048,7 +9048,7 @@
         <v>1</v>
       </c>
       <c r="H121" t="n">
-        <v>67478.85000000001</v>
+        <v>67473.71000000001</v>
       </c>
       <c r="I121" t="n">
         <v>1.78</v>
@@ -9116,7 +9116,7 @@
         <v>1</v>
       </c>
       <c r="H122" t="n">
-        <v>36541.1</v>
+        <v>36538.26</v>
       </c>
       <c r="I122" t="n">
         <v>1.74</v>
@@ -9184,7 +9184,7 @@
         <v>1</v>
       </c>
       <c r="H123" t="n">
-        <v>52493.36</v>
+        <v>52490.25</v>
       </c>
       <c r="I123" t="n">
         <v>2.28</v>
@@ -9252,7 +9252,7 @@
         <v>1</v>
       </c>
       <c r="H124" t="n">
-        <v>41081.76</v>
+        <v>41079.33</v>
       </c>
       <c r="I124" t="n">
         <v>2.28</v>
@@ -9320,7 +9320,7 @@
         <v>1</v>
       </c>
       <c r="H125" t="n">
-        <v>164574.56</v>
+        <v>164564.01</v>
       </c>
       <c r="I125" t="n">
         <v>2.11</v>
@@ -9388,7 +9388,7 @@
         <v>1</v>
       </c>
       <c r="H126" t="n">
-        <v>67517.77</v>
+        <v>67513.44</v>
       </c>
       <c r="I126" t="n">
         <v>2.11</v>
@@ -9456,7 +9456,7 @@
         <v>1</v>
       </c>
       <c r="H127" t="n">
-        <v>34125.6</v>
+        <v>34123.44</v>
       </c>
       <c r="I127" t="n">
         <v>2.13</v>
@@ -9524,7 +9524,7 @@
         <v>1</v>
       </c>
       <c r="H128" t="n">
-        <v>86507.14</v>
+        <v>86501.60000000001</v>
       </c>
       <c r="I128" t="n">
         <v>2.11</v>
@@ -9592,7 +9592,7 @@
         <v>1</v>
       </c>
       <c r="H129" t="n">
-        <v>51188.4</v>
+        <v>51185.16</v>
       </c>
       <c r="I129" t="n">
         <v>2.13</v>
@@ -9660,7 +9660,7 @@
         <v>1</v>
       </c>
       <c r="H130" t="n">
-        <v>151414.04</v>
+        <v>151404.99</v>
       </c>
       <c r="I130" t="n">
         <v>2.26</v>
@@ -9728,7 +9728,7 @@
         <v>1</v>
       </c>
       <c r="H131" t="n">
-        <v>117515.38</v>
+        <v>117508.35</v>
       </c>
       <c r="I131" t="n">
         <v>2.26</v>
@@ -9796,7 +9796,7 @@
         <v>1</v>
       </c>
       <c r="H132" t="n">
-        <v>99436.09</v>
+        <v>99430.14</v>
       </c>
       <c r="I132" t="n">
         <v>2.26</v>
@@ -9864,7 +9864,7 @@
         <v>1</v>
       </c>
       <c r="H133" t="n">
-        <v>40678.4</v>
+        <v>40675.97</v>
       </c>
       <c r="I133" t="n">
         <v>2.26</v>
@@ -9932,7 +9932,7 @@
         <v>1</v>
       </c>
       <c r="H134" t="n">
-        <v>15819.38</v>
+        <v>15818.43</v>
       </c>
       <c r="I134" t="n">
         <v>2.26</v>
@@ -10000,7 +10000,7 @@
         <v>1</v>
       </c>
       <c r="H135" t="n">
-        <v>36158.58</v>
+        <v>36156.41</v>
       </c>
       <c r="I135" t="n">
         <v>2.26</v>
@@ -10179,7 +10179,7 @@
         <v>3093.6</v>
       </c>
       <c r="I2" t="n">
-        <v>129942.5</v>
+        <v>129942.48</v>
       </c>
       <c r="J2" t="n">
         <v>100.39</v>
@@ -10231,7 +10231,7 @@
         <v>183.2</v>
       </c>
       <c r="I3" t="n">
-        <v>13466.27</v>
+        <v>13466.23</v>
       </c>
       <c r="J3" t="n">
         <v>322.81</v>
@@ -10289,7 +10289,7 @@
         <v>183.2</v>
       </c>
       <c r="I4" t="n">
-        <v>20520.04</v>
+        <v>20519.97</v>
       </c>
       <c r="J4" t="n">
         <v>483.47</v>
@@ -10347,7 +10347,7 @@
         <v>183.2</v>
       </c>
       <c r="I5" t="n">
-        <v>11542.52</v>
+        <v>11542.48</v>
       </c>
       <c r="J5" t="n">
         <v>416.21</v>
@@ -10405,7 +10405,7 @@
         <v>3288.6</v>
       </c>
       <c r="I6" t="n">
-        <v>126622.1</v>
+        <v>126622.08</v>
       </c>
       <c r="J6" t="n">
         <v>255.89</v>
@@ -10457,7 +10457,7 @@
         <v>203.1</v>
       </c>
       <c r="I7" t="n">
-        <v>31279.76</v>
+        <v>31279.67</v>
       </c>
       <c r="J7" t="n">
         <v>538.08</v>
@@ -10515,7 +10515,7 @@
         <v>177.03</v>
       </c>
       <c r="I8" t="n">
-        <v>24167.2</v>
+        <v>24167.12</v>
       </c>
       <c r="J8" t="n">
         <v>1162.1</v>
@@ -10573,7 +10573,7 @@
         <v>177.03</v>
       </c>
       <c r="I9" t="n">
-        <v>17350.81</v>
+        <v>17350.75</v>
       </c>
       <c r="J9" t="n">
         <v>1251.46</v>
@@ -10631,7 +10631,7 @@
         <v>177.03</v>
       </c>
       <c r="I10" t="n">
-        <v>19209.83</v>
+        <v>19209.76</v>
       </c>
       <c r="J10" t="n">
         <v>767.52</v>
@@ -10689,7 +10689,7 @@
         <v>177.03</v>
       </c>
       <c r="I11" t="n">
-        <v>4647.54</v>
+        <v>4647.52</v>
       </c>
       <c r="J11" t="n">
         <v>955.4400000000001</v>
@@ -10747,7 +10747,7 @@
         <v>2953.6</v>
       </c>
       <c r="I12" t="n">
-        <v>93046.5</v>
+        <v>93046.48</v>
       </c>
       <c r="J12" t="n">
         <v>617.75</v>
@@ -10799,7 +10799,7 @@
         <v>2953.6</v>
       </c>
       <c r="I13" t="n">
-        <v>87877.25</v>
+        <v>87877.23</v>
       </c>
       <c r="J13" t="n">
         <v>684.9400000000001</v>
@@ -10851,7 +10851,7 @@
         <v>174.74</v>
       </c>
       <c r="I14" t="n">
-        <v>37921.81</v>
+        <v>37921.69</v>
       </c>
       <c r="J14" t="n">
         <v>448.61</v>
@@ -10909,7 +10909,7 @@
         <v>174.74</v>
       </c>
       <c r="I15" t="n">
-        <v>10397.92</v>
+        <v>10397.88</v>
       </c>
       <c r="J15" t="n">
         <v>358.09</v>
@@ -10967,7 +10967,7 @@
         <v>651.11</v>
       </c>
       <c r="I16" t="n">
-        <v>66092.91</v>
+        <v>66092.86</v>
       </c>
       <c r="J16" t="n">
         <v>534.23</v>
@@ -11025,7 +11025,7 @@
         <v>651.11</v>
       </c>
       <c r="I17" t="n">
-        <v>47860.39</v>
+        <v>47860.34</v>
       </c>
       <c r="J17" t="n">
         <v>758.5700000000001</v>
@@ -11083,7 +11083,7 @@
         <v>651.11</v>
       </c>
       <c r="I18" t="n">
-        <v>54697.58</v>
+        <v>54697.54</v>
       </c>
       <c r="J18" t="n">
         <v>483.91</v>
@@ -11141,7 +11141,7 @@
         <v>651.11</v>
       </c>
       <c r="I19" t="n">
-        <v>31906.92</v>
+        <v>31906.9</v>
       </c>
       <c r="J19" t="n">
         <v>488.03</v>
@@ -11199,7 +11199,7 @@
         <v>651.11</v>
       </c>
       <c r="I20" t="n">
-        <v>34185.99</v>
+        <v>34185.96</v>
       </c>
       <c r="J20" t="n">
         <v>407.1</v>
@@ -11257,7 +11257,7 @@
         <v>233.43</v>
       </c>
       <c r="I21" t="n">
-        <v>58013.48</v>
+        <v>58013.34</v>
       </c>
       <c r="J21" t="n">
         <v>323.36</v>
@@ -11315,7 +11315,7 @@
         <v>233.43</v>
       </c>
       <c r="I22" t="n">
-        <v>17976.01</v>
+        <v>17975.97</v>
       </c>
       <c r="J22" t="n">
         <v>308.79</v>
@@ -11373,7 +11373,7 @@
         <v>233.43</v>
       </c>
       <c r="I23" t="n">
-        <v>10622.19</v>
+        <v>10622.16</v>
       </c>
       <c r="J23" t="n">
         <v>447.3</v>
@@ -11431,7 +11431,7 @@
         <v>233.43</v>
       </c>
       <c r="I24" t="n">
-        <v>8988</v>
+        <v>8987.98</v>
       </c>
       <c r="J24" t="n">
         <v>459</v>
@@ -11489,7 +11489,7 @@
         <v>233.43</v>
       </c>
       <c r="I25" t="n">
-        <v>11439.28</v>
+        <v>11439.25</v>
       </c>
       <c r="J25" t="n">
         <v>306.91</v>
@@ -11547,7 +11547,7 @@
         <v>3211.36</v>
       </c>
       <c r="I26" t="n">
-        <v>112407.19</v>
+        <v>112407.17</v>
       </c>
       <c r="J26" t="n">
         <v>315.98</v>
@@ -11599,7 +11599,7 @@
         <v>220.16</v>
       </c>
       <c r="I27" t="n">
-        <v>32365.95</v>
+        <v>32365.87</v>
       </c>
       <c r="J27" t="n">
         <v>117.11</v>
@@ -11657,7 +11657,7 @@
         <v>220.16</v>
       </c>
       <c r="I28" t="n">
-        <v>13100.5</v>
+        <v>13100.47</v>
       </c>
       <c r="J28" t="n">
         <v>106.12</v>
@@ -11715,7 +11715,7 @@
         <v>3081.36</v>
       </c>
       <c r="I29" t="n">
-        <v>204927.91</v>
+        <v>204927.88</v>
       </c>
       <c r="J29" t="n">
         <v>64.55</v>
@@ -11767,7 +11767,7 @@
         <v>309.7</v>
       </c>
       <c r="I30" t="n">
-        <v>28185</v>
+        <v>28184.95</v>
       </c>
       <c r="J30" t="n">
         <v>106.06</v>
@@ -11825,7 +11825,7 @@
         <v>301.25</v>
       </c>
       <c r="I31" t="n">
-        <v>23198.1</v>
+        <v>23198.06</v>
       </c>
       <c r="J31" t="n">
         <v>80.93000000000001</v>
@@ -11883,7 +11883,7 @@
         <v>2818.79</v>
       </c>
       <c r="I32" t="n">
-        <v>118399.23</v>
+        <v>118399.21</v>
       </c>
       <c r="J32" t="n">
         <v>98.78</v>
@@ -11935,7 +11935,7 @@
         <v>3308.79</v>
       </c>
       <c r="I33" t="n">
-        <v>162144.5</v>
+        <v>162144.47</v>
       </c>
       <c r="J33" t="n">
         <v>139.33</v>
@@ -11987,7 +11987,7 @@
         <v>277.28</v>
       </c>
       <c r="I34" t="n">
-        <v>85410.10000000001</v>
+        <v>85409.92999999999</v>
       </c>
       <c r="J34" t="n">
         <v>364.01</v>
@@ -12045,7 +12045,7 @@
         <v>277.28</v>
       </c>
       <c r="I35" t="n">
-        <v>50469.61</v>
+        <v>50469.5</v>
       </c>
       <c r="J35" t="n">
         <v>428.56</v>
@@ -12103,7 +12103,7 @@
         <v>277.28</v>
       </c>
       <c r="I36" t="n">
-        <v>42705.05</v>
+        <v>42704.96</v>
       </c>
       <c r="J36" t="n">
         <v>280.66</v>
@@ -12161,7 +12161,7 @@
         <v>277.28</v>
       </c>
       <c r="I37" t="n">
-        <v>32028.79</v>
+        <v>32028.72</v>
       </c>
       <c r="J37" t="n">
         <v>390.59</v>
@@ -12219,7 +12219,7 @@
         <v>277.28</v>
       </c>
       <c r="I38" t="n">
-        <v>26205.37</v>
+        <v>26205.32</v>
       </c>
       <c r="J38" t="n">
         <v>405.44</v>
@@ -12277,7 +12277,7 @@
         <v>277.28</v>
       </c>
       <c r="I39" t="n">
-        <v>45616.76</v>
+        <v>45616.67</v>
       </c>
       <c r="J39" t="n">
         <v>698.29</v>
@@ -12335,7 +12335,7 @@
         <v>277.28</v>
       </c>
       <c r="I40" t="n">
-        <v>37852.2</v>
+        <v>37852.13</v>
       </c>
       <c r="J40" t="n">
         <v>544.61</v>
@@ -12393,7 +12393,7 @@
         <v>277.28</v>
       </c>
       <c r="I41" t="n">
-        <v>23293.66</v>
+        <v>23293.62</v>
       </c>
       <c r="J41" t="n">
         <v>560.1</v>
@@ -12451,7 +12451,7 @@
         <v>277.28</v>
       </c>
       <c r="I42" t="n">
-        <v>21352.53</v>
+        <v>21352.48</v>
       </c>
       <c r="J42" t="n">
         <v>494.37</v>
@@ -12509,7 +12509,7 @@
         <v>421.97</v>
       </c>
       <c r="I43" t="n">
-        <v>35448.33</v>
+        <v>35448.28</v>
       </c>
       <c r="J43" t="n">
         <v>532.85</v>
@@ -12567,7 +12567,7 @@
         <v>421.97</v>
       </c>
       <c r="I44" t="n">
-        <v>22155.21</v>
+        <v>22155.18</v>
       </c>
       <c r="J44" t="n">
         <v>426.83</v>
@@ -12625,7 +12625,7 @@
         <v>3763.79</v>
       </c>
       <c r="I45" t="n">
-        <v>237138.95</v>
+        <v>237138.92</v>
       </c>
       <c r="J45" t="n">
         <v>460.47</v>
@@ -12677,7 +12677,7 @@
         <v>3203.79</v>
       </c>
       <c r="I46" t="n">
-        <v>145784.84</v>
+        <v>145784.81</v>
       </c>
       <c r="J46" t="n">
         <v>538.6799999999999</v>
@@ -12729,7 +12729,7 @@
         <v>3763.79</v>
       </c>
       <c r="I47" t="n">
-        <v>144918.25</v>
+        <v>144918.23</v>
       </c>
       <c r="J47" t="n">
         <v>395.68</v>
@@ -12781,7 +12781,7 @@
         <v>3508.71</v>
       </c>
       <c r="I48" t="n">
-        <v>196504.47</v>
+        <v>196504.41</v>
       </c>
       <c r="J48" t="n">
         <v>201.21</v>
@@ -12833,7 +12833,7 @@
         <v>2988.71</v>
       </c>
       <c r="I49" t="n">
-        <v>198766.1</v>
+        <v>198766.02</v>
       </c>
       <c r="J49" t="n">
         <v>53.72</v>
@@ -12885,7 +12885,7 @@
         <v>3053.71</v>
       </c>
       <c r="I50" t="n">
-        <v>224466.76</v>
+        <v>224466.67</v>
       </c>
       <c r="J50" t="n">
         <v>94.98999999999999</v>
@@ -12937,7 +12937,7 @@
         <v>3211.36</v>
       </c>
       <c r="I51" t="n">
-        <v>146129.34</v>
+        <v>146129.32</v>
       </c>
       <c r="J51" t="n">
         <v>120.54</v>
@@ -12989,7 +12989,7 @@
         <v>3211.36</v>
       </c>
       <c r="I52" t="n">
-        <v>123647.91</v>
+        <v>123647.88</v>
       </c>
       <c r="J52" t="n">
         <v>130.5</v>
@@ -13041,7 +13041,7 @@
         <v>454.14</v>
       </c>
       <c r="I53" t="n">
-        <v>54047.26</v>
+        <v>54047.2</v>
       </c>
       <c r="J53" t="n">
         <v>477.86</v>
@@ -13099,7 +13099,7 @@
         <v>454.14</v>
       </c>
       <c r="I54" t="n">
-        <v>14306.63</v>
+        <v>14306.61</v>
       </c>
       <c r="J54" t="n">
         <v>482.12</v>
@@ -13157,7 +13157,7 @@
         <v>454.14</v>
       </c>
       <c r="I55" t="n">
-        <v>10332.57</v>
+        <v>10332.55</v>
       </c>
       <c r="J55" t="n">
         <v>480.24</v>
@@ -13215,7 +13215,7 @@
         <v>454.14</v>
       </c>
       <c r="I56" t="n">
-        <v>8742.940000000001</v>
+        <v>8742.93</v>
       </c>
       <c r="J56" t="n">
         <v>481.26</v>
@@ -13273,7 +13273,7 @@
         <v>454.14</v>
       </c>
       <c r="I57" t="n">
-        <v>7948.13</v>
+        <v>7948.12</v>
       </c>
       <c r="J57" t="n">
         <v>412.79</v>
@@ -13331,7 +13331,7 @@
         <v>325.17</v>
       </c>
       <c r="I58" t="n">
-        <v>66015.7</v>
+        <v>66015.58</v>
       </c>
       <c r="J58" t="n">
         <v>311.37</v>
@@ -13389,7 +13389,7 @@
         <v>325.17</v>
       </c>
       <c r="I59" t="n">
-        <v>52357.28</v>
+        <v>52357.19</v>
       </c>
       <c r="J59" t="n">
         <v>94.95999999999999</v>
@@ -13447,7 +13447,7 @@
         <v>333.23</v>
       </c>
       <c r="I60" t="n">
-        <v>22161.67</v>
+        <v>22161.63</v>
       </c>
       <c r="J60" t="n">
         <v>182.8</v>
@@ -13505,7 +13505,7 @@
         <v>325.17</v>
       </c>
       <c r="I61" t="n">
-        <v>19349.43</v>
+        <v>19349.4</v>
       </c>
       <c r="J61" t="n">
         <v>175.95</v>
@@ -13563,7 +13563,7 @@
         <v>333.23</v>
       </c>
       <c r="I62" t="n">
-        <v>9331.23</v>
+        <v>9331.209999999999</v>
       </c>
       <c r="J62" t="n">
         <v>205.12</v>
@@ -13621,7 +13621,7 @@
         <v>333.23</v>
       </c>
       <c r="I63" t="n">
-        <v>16329.65</v>
+        <v>16329.62</v>
       </c>
       <c r="J63" t="n">
         <v>368.78</v>
@@ -13679,7 +13679,7 @@
         <v>342.73</v>
       </c>
       <c r="I64" t="n">
-        <v>27592.42</v>
+        <v>27592.38</v>
       </c>
       <c r="J64" t="n">
         <v>240.83</v>
@@ -13737,7 +13737,7 @@
         <v>342.73</v>
       </c>
       <c r="I65" t="n">
-        <v>21594.07</v>
+        <v>21594.03</v>
       </c>
       <c r="J65" t="n">
         <v>189.94</v>
@@ -13795,7 +13795,7 @@
         <v>293.48</v>
       </c>
       <c r="I66" t="n">
-        <v>80127.89</v>
+        <v>80127.74000000001</v>
       </c>
       <c r="J66" t="n">
         <v>328.7</v>
@@ -13853,7 +13853,7 @@
         <v>293.48</v>
       </c>
       <c r="I67" t="n">
-        <v>32872.98</v>
+        <v>32872.92</v>
       </c>
       <c r="J67" t="n">
         <v>328.88</v>
@@ -13911,7 +13911,7 @@
         <v>300.03</v>
       </c>
       <c r="I68" t="n">
-        <v>16803.21</v>
+        <v>16803.18</v>
       </c>
       <c r="J68" t="n">
         <v>369.95</v>
@@ -13969,7 +13969,7 @@
         <v>293.48</v>
       </c>
       <c r="I69" t="n">
-        <v>42118.51</v>
+        <v>42118.43</v>
       </c>
       <c r="J69" t="n">
         <v>215.37</v>
@@ -14027,7 +14027,7 @@
         <v>300.03</v>
       </c>
       <c r="I70" t="n">
-        <v>25204.82</v>
+        <v>25204.77</v>
       </c>
       <c r="J70" t="n">
         <v>445.5</v>
@@ -14085,7 +14085,7 @@
         <v>336.33</v>
       </c>
       <c r="I71" t="n">
-        <v>78876.52</v>
+        <v>78876.39</v>
       </c>
       <c r="J71" t="n">
         <v>357.34</v>
@@ -14143,7 +14143,7 @@
         <v>336.33</v>
       </c>
       <c r="I72" t="n">
-        <v>61217.6</v>
+        <v>61217.5</v>
       </c>
       <c r="J72" t="n">
         <v>513.78</v>
@@ -14201,7 +14201,7 @@
         <v>336.33</v>
       </c>
       <c r="I73" t="n">
-        <v>51799.51</v>
+        <v>51799.42</v>
       </c>
       <c r="J73" t="n">
         <v>577.77</v>
@@ -14259,7 +14259,7 @@
         <v>336.33</v>
       </c>
       <c r="I74" t="n">
-        <v>21190.71</v>
+        <v>21190.67</v>
       </c>
       <c r="J74" t="n">
         <v>447.68</v>
@@ -14317,7 +14317,7 @@
         <v>336.33</v>
       </c>
       <c r="I75" t="n">
-        <v>8240.83</v>
+        <v>8240.82</v>
       </c>
       <c r="J75" t="n">
         <v>267.72</v>
@@ -14375,7 +14375,7 @@
         <v>336.33</v>
       </c>
       <c r="I76" t="n">
-        <v>18836.18</v>
+        <v>18836.15</v>
       </c>
       <c r="J76" t="n">
         <v>370.08</v>
@@ -14427,13 +14427,13 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>587.5544</v>
+        <v>588.0504</v>
       </c>
       <c r="H77" t="n">
         <v>55.64</v>
       </c>
       <c r="I77" t="n">
-        <v>32691.99</v>
+        <v>32716.97</v>
       </c>
       <c r="J77" t="n">
         <v>4.28</v>
@@ -14482,10 +14482,10 @@
         <v>462.0396</v>
       </c>
       <c r="H78" t="n">
-        <v>60.04</v>
+        <v>60.03</v>
       </c>
       <c r="I78" t="n">
-        <v>27738.74</v>
+        <v>27738.47</v>
       </c>
       <c r="J78" t="n">
         <v>13.54</v>
@@ -14537,7 +14537,7 @@
         <v>54.32</v>
       </c>
       <c r="I79" t="n">
-        <v>11598.56</v>
+        <v>11598.44</v>
       </c>
       <c r="J79" t="n">
         <v>1.51</v>
@@ -14589,7 +14589,7 @@
         <v>56.12</v>
       </c>
       <c r="I80" t="n">
-        <v>10606.96</v>
+        <v>10606.85</v>
       </c>
       <c r="J80" t="n">
         <v>5.29</v>
@@ -14641,7 +14641,7 @@
         <v>58.93</v>
       </c>
       <c r="I81" t="n">
-        <v>7838.18</v>
+        <v>7838.11</v>
       </c>
       <c r="J81" t="n">
         <v>11.21</v>
@@ -14693,7 +14693,7 @@
         <v>121.89</v>
       </c>
       <c r="I82" t="n">
-        <v>20052.9</v>
+        <v>20052.8</v>
       </c>
       <c r="J82" t="n">
         <v>103.3</v>
@@ -14745,7 +14745,7 @@
         <v>228.91</v>
       </c>
       <c r="I83" t="n">
-        <v>15223.63</v>
+        <v>15223.59</v>
       </c>
       <c r="J83" t="n">
         <v>218.82</v>
@@ -14797,7 +14797,7 @@
         <v>171.53</v>
       </c>
       <c r="I84" t="n">
-        <v>22815.78</v>
+        <v>22815.7</v>
       </c>
       <c r="J84" t="n">
         <v>183.69</v>
@@ -14849,7 +14849,7 @@
         <v>262.6</v>
       </c>
       <c r="I85" t="n">
-        <v>53312.65</v>
+        <v>53312.54</v>
       </c>
       <c r="J85" t="n">
         <v>331.17</v>
@@ -14895,13 +14895,13 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>656.3203999999999</v>
+        <v>658.0564000000001</v>
       </c>
       <c r="H86" t="n">
-        <v>106.87</v>
+        <v>106.86</v>
       </c>
       <c r="I86" t="n">
-        <v>70143.8</v>
+        <v>70320.95</v>
       </c>
       <c r="J86" t="n">
         <v>1.06</v>
@@ -14953,7 +14953,7 @@
         <v>170.55</v>
       </c>
       <c r="I87" t="n">
-        <v>32236.32</v>
+        <v>32236.22</v>
       </c>
       <c r="J87" t="n">
         <v>113.39</v>
@@ -15005,7 +15005,7 @@
         <v>213.85</v>
       </c>
       <c r="I88" t="n">
-        <v>23205.22</v>
+        <v>23205.16</v>
       </c>
       <c r="J88" t="n">
         <v>129.6</v>
@@ -15057,7 +15057,7 @@
         <v>274.57</v>
       </c>
       <c r="I89" t="n">
-        <v>34598.92</v>
+        <v>34598.85</v>
       </c>
       <c r="J89" t="n">
         <v>209.49</v>
@@ -15109,7 +15109,7 @@
         <v>164.01</v>
       </c>
       <c r="I90" t="n">
-        <v>13203.88</v>
+        <v>13203.84</v>
       </c>
       <c r="J90" t="n">
         <v>101.42</v>
@@ -15161,7 +15161,7 @@
         <v>139.45</v>
       </c>
       <c r="I91" t="n">
-        <v>46858.55</v>
+        <v>46858.36</v>
       </c>
       <c r="J91" t="n">
         <v>1.39</v>
@@ -15213,7 +15213,7 @@
         <v>212.96</v>
       </c>
       <c r="I92" t="n">
-        <v>53670.71</v>
+        <v>53670.42</v>
       </c>
       <c r="J92" t="n">
         <v>122.66</v>
@@ -15265,7 +15265,7 @@
         <v>190.16</v>
       </c>
       <c r="I93" t="n">
-        <v>31949.66</v>
+        <v>31949.47</v>
       </c>
       <c r="J93" t="n">
         <v>80.92</v>
@@ -15317,7 +15317,7 @@
         <v>279.07</v>
       </c>
       <c r="I94" t="n">
-        <v>37119.88</v>
+        <v>37119.73</v>
       </c>
       <c r="J94" t="n">
         <v>166.27</v>
@@ -15369,7 +15369,7 @@
         <v>325.16</v>
       </c>
       <c r="I95" t="n">
-        <v>46664.36</v>
+        <v>46664.2</v>
       </c>
       <c r="J95" t="n">
         <v>226.91</v>
@@ -15418,10 +15418,10 @@
         <v>101.5087</v>
       </c>
       <c r="H96" t="n">
-        <v>239.96</v>
+        <v>239.95</v>
       </c>
       <c r="I96" t="n">
-        <v>24357.59</v>
+        <v>24357.48</v>
       </c>
       <c r="J96" t="n">
         <v>114.8</v>
@@ -15470,10 +15470,10 @@
         <v>112.0096</v>
       </c>
       <c r="H97" t="n">
-        <v>259.15</v>
+        <v>259.14</v>
       </c>
       <c r="I97" t="n">
-        <v>29026.81</v>
+        <v>29026.68</v>
       </c>
       <c r="J97" t="n">
         <v>140.05</v>
@@ -15525,7 +15525,7 @@
         <v>342.49</v>
       </c>
       <c r="I98" t="n">
-        <v>100702.14</v>
+        <v>100701.8</v>
       </c>
       <c r="J98" t="n">
         <v>249.72</v>
@@ -15577,7 +15577,7 @@
         <v>375.77</v>
       </c>
       <c r="I99" t="n">
-        <v>56557.89</v>
+        <v>56557.72</v>
       </c>
       <c r="J99" t="n">
         <v>293.5</v>
@@ -15629,7 +15629,7 @@
         <v>358.96</v>
       </c>
       <c r="I100" t="n">
-        <v>38950.12</v>
+        <v>38950</v>
       </c>
       <c r="J100" t="n">
         <v>271.38</v>
@@ -15681,7 +15681,7 @@
         <v>306.96</v>
       </c>
       <c r="I101" t="n">
-        <v>29009.95</v>
+        <v>29009.85</v>
       </c>
       <c r="J101" t="n">
         <v>202.96</v>
@@ -15733,7 +15733,7 @@
         <v>215.22</v>
       </c>
       <c r="I102" t="n">
-        <v>59514.04</v>
+        <v>59513.73</v>
       </c>
       <c r="J102" t="n">
         <v>126.8</v>
@@ -15785,7 +15785,7 @@
         <v>199.41</v>
       </c>
       <c r="I103" t="n">
-        <v>30712.35</v>
+        <v>30712.17</v>
       </c>
       <c r="J103" t="n">
         <v>97.86</v>
@@ -15837,7 +15837,7 @@
         <v>250.22</v>
       </c>
       <c r="I104" t="n">
-        <v>31530.84</v>
+        <v>31530.7</v>
       </c>
       <c r="J104" t="n">
         <v>128.31</v>
@@ -15886,10 +15886,10 @@
         <v>136.5117</v>
       </c>
       <c r="H105" t="n">
-        <v>280.27</v>
+        <v>280.26</v>
       </c>
       <c r="I105" t="n">
-        <v>38259.6</v>
+        <v>38259.45</v>
       </c>
       <c r="J105" t="n">
         <v>167.84</v>
@@ -15941,7 +15941,7 @@
         <v>274.37</v>
       </c>
       <c r="I106" t="n">
-        <v>22088.56</v>
+        <v>22088.47</v>
       </c>
       <c r="J106" t="n">
         <v>160.08</v>
@@ -15993,7 +15993,7 @@
         <v>227.8</v>
       </c>
       <c r="I107" t="n">
-        <v>22326.64</v>
+        <v>22326.53</v>
       </c>
       <c r="J107" t="n">
         <v>98.81</v>
@@ -16045,7 +16045,7 @@
         <v>144.86</v>
       </c>
       <c r="I108" t="n">
-        <v>56788.9</v>
+        <v>56788.45</v>
       </c>
       <c r="J108" t="n">
         <v>2.42</v>
@@ -16094,10 +16094,10 @@
         <v>119.0102</v>
       </c>
       <c r="H109" t="n">
-        <v>195.66</v>
+        <v>195.65</v>
       </c>
       <c r="I109" t="n">
-        <v>23284.98</v>
+        <v>23284.84</v>
       </c>
       <c r="J109" t="n">
         <v>56.51</v>
@@ -16149,7 +16149,7 @@
         <v>201.38</v>
       </c>
       <c r="I110" t="n">
-        <v>21851.4</v>
+        <v>21851.28</v>
       </c>
       <c r="J110" t="n">
         <v>64.04000000000001</v>
@@ -16201,7 +16201,7 @@
         <v>179.58</v>
       </c>
       <c r="I111" t="n">
-        <v>13828.95</v>
+        <v>13828.86</v>
       </c>
       <c r="J111" t="n">
         <v>35.36</v>
@@ -16250,10 +16250,10 @@
         <v>91.0078</v>
       </c>
       <c r="H112" t="n">
-        <v>161.94</v>
+        <v>161.93</v>
       </c>
       <c r="I112" t="n">
-        <v>14737.4</v>
+        <v>14737.29</v>
       </c>
       <c r="J112" t="n">
         <v>29.25</v>
@@ -16305,7 +16305,7 @@
         <v>191.21</v>
       </c>
       <c r="I113" t="n">
-        <v>38819.88</v>
+        <v>38819.65</v>
       </c>
       <c r="J113" t="n">
         <v>82.84999999999999</v>
@@ -16354,10 +16354,10 @@
         <v>143.5123</v>
       </c>
       <c r="H114" t="n">
-        <v>186.15</v>
+        <v>186.14</v>
       </c>
       <c r="I114" t="n">
-        <v>26714.14</v>
+        <v>26713.98</v>
       </c>
       <c r="J114" t="n">
         <v>73.56999999999999</v>
@@ -16409,7 +16409,7 @@
         <v>182.3</v>
       </c>
       <c r="I115" t="n">
-        <v>29990.88</v>
+        <v>29990.69</v>
       </c>
       <c r="J115" t="n">
         <v>66.53</v>
@@ -16461,7 +16461,7 @@
         <v>227.78</v>
       </c>
       <c r="I116" t="n">
-        <v>19135.2</v>
+        <v>19135.11</v>
       </c>
       <c r="J116" t="n">
         <v>98.78</v>
@@ -16513,7 +16513,7 @@
         <v>224.8</v>
       </c>
       <c r="I117" t="n">
-        <v>58229.08</v>
+        <v>58228.79</v>
       </c>
       <c r="J117" t="n">
         <v>144.34</v>
@@ -16565,7 +16565,7 @@
         <v>206.84</v>
       </c>
       <c r="I118" t="n">
-        <v>33303.66</v>
+        <v>33303.47</v>
       </c>
       <c r="J118" t="n">
         <v>111.45</v>
@@ -16617,7 +16617,7 @@
         <v>256.11</v>
       </c>
       <c r="I119" t="n">
-        <v>29583.62</v>
+        <v>29583.49</v>
       </c>
       <c r="J119" t="n">
         <v>136.06</v>
@@ -16669,7 +16669,7 @@
         <v>243.41</v>
       </c>
       <c r="I120" t="n">
-        <v>24708.1</v>
+        <v>24707.99</v>
       </c>
       <c r="J120" t="n">
         <v>178.4</v>
@@ -16721,7 +16721,7 @@
         <v>269.42</v>
       </c>
       <c r="I121" t="n">
-        <v>23576.35</v>
+        <v>23576.25</v>
       </c>
       <c r="J121" t="n">
         <v>153.57</v>
@@ -16767,13 +16767,13 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>378.1564</v>
+        <v>378.0324</v>
       </c>
       <c r="H122" t="n">
         <v>291.52</v>
       </c>
       <c r="I122" t="n">
-        <v>110239.76</v>
+        <v>110203.97</v>
       </c>
       <c r="J122" t="n">
         <v>334.85</v>
@@ -16825,7 +16825,7 @@
         <v>236.2</v>
       </c>
       <c r="I123" t="n">
-        <v>51258.98</v>
+        <v>51258.86</v>
       </c>
       <c r="J123" t="n">
         <v>233.57</v>
@@ -16877,7 +16877,7 @@
         <v>329.86</v>
       </c>
       <c r="I124" t="n">
-        <v>39256.83</v>
+        <v>39256.76</v>
       </c>
       <c r="J124" t="n">
         <v>282.24</v>
@@ -16929,7 +16929,7 @@
         <v>385.21</v>
       </c>
       <c r="I125" t="n">
-        <v>41799.07</v>
+        <v>41799.01</v>
       </c>
       <c r="J125" t="n">
         <v>355.07</v>
@@ -16981,7 +16981,7 @@
         <v>333.64</v>
       </c>
       <c r="I126" t="n">
-        <v>32699.35</v>
+        <v>32699.3</v>
       </c>
       <c r="J126" t="n">
         <v>287.21</v>
@@ -17033,7 +17033,7 @@
         <v>194.93</v>
       </c>
       <c r="I127" t="n">
-        <v>62771.83</v>
+        <v>62771.65</v>
       </c>
       <c r="J127" t="n">
         <v>31.5</v>
@@ -17085,7 +17085,7 @@
         <v>171.62</v>
       </c>
       <c r="I128" t="n">
-        <v>36643.34</v>
+        <v>36643.22</v>
       </c>
       <c r="J128" t="n">
         <v>1.35</v>
@@ -17137,7 +17137,7 @@
         <v>198.01</v>
       </c>
       <c r="I129" t="n">
-        <v>26338.17</v>
+        <v>26338.09</v>
       </c>
       <c r="J129" t="n">
         <v>36.5</v>
@@ -17189,7 +17189,7 @@
         <v>187.81</v>
       </c>
       <c r="I130" t="n">
-        <v>13805.46</v>
+        <v>13805.42</v>
       </c>
       <c r="J130" t="n">
         <v>19.98</v>
@@ -17241,7 +17241,7 @@
         <v>3448.6</v>
       </c>
       <c r="I131" t="n">
-        <v>289707.56</v>
+        <v>289707.51</v>
       </c>
       <c r="J131" t="n">
         <v>190.55</v>
@@ -17293,7 +17293,7 @@
         <v>3448.6</v>
       </c>
       <c r="I132" t="n">
-        <v>506988.23</v>
+        <v>506988.14</v>
       </c>
       <c r="J132" t="n">
         <v>118.45</v>
@@ -17345,7 +17345,7 @@
         <v>3448.6</v>
       </c>
       <c r="I133" t="n">
-        <v>193138.37</v>
+        <v>193138.34</v>
       </c>
       <c r="J133" t="n">
         <v>86.87</v>
@@ -17397,7 +17397,7 @@
         <v>3533.79</v>
       </c>
       <c r="I134" t="n">
-        <v>507142.01</v>
+        <v>507141.93</v>
       </c>
       <c r="J134" t="n">
         <v>139.86</v>
@@ -17449,7 +17449,7 @@
         <v>3533.79</v>
       </c>
       <c r="I135" t="n">
-        <v>346340.88</v>
+        <v>346340.83</v>
       </c>
       <c r="J135" t="n">
         <v>75.73999999999999</v>
@@ -17563,16 +17563,16 @@
         <v>1034000</v>
       </c>
       <c r="D5" t="n">
-        <v>3617.1</v>
+        <v>3619.3</v>
       </c>
       <c r="E5" t="n">
-        <v>3617.1</v>
+        <v>3619.3</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>2936442.81</v>
+        <v>2937196.26</v>
       </c>
       <c r="H5" t="n">
         <v>2.84</v>
@@ -17603,7 +17603,7 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>2053521.77</v>
+        <v>2053395.72</v>
       </c>
       <c r="H6" t="n">
         <v>2.22</v>
@@ -17634,7 +17634,7 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>1868523.89</v>
+        <v>1868388.19</v>
       </c>
       <c r="H7" t="n">
         <v>1.88</v>
@@ -17656,16 +17656,16 @@
         <v>967500</v>
       </c>
       <c r="D8" t="n">
-        <v>3386.7</v>
+        <v>3386.5</v>
       </c>
       <c r="E8" t="n">
-        <v>3386.7</v>
+        <v>3386.5</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>2086059.62</v>
+        <v>2085854.47</v>
       </c>
       <c r="H8" t="n">
         <v>2.16</v>
@@ -17696,7 +17696,7 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>4374496.66</v>
+        <v>4374364.98</v>
       </c>
       <c r="H9" t="n">
         <v>4.49</v>
@@ -17741,7 +17741,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>One-off cost 0 PGK · annual change -1,950,104 PGK · payback n/a years</t>
+          <t>One-off cost 0 PGK · annual change 2,075,021 PGK · payback n/a years</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-4.xlsx
+++ b/docs/app/api/files/results-4.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: March · solver HiGHS Optimal · run 2026-09-28 18:35 UTC · 66 ms</t>
+          <t>Conditions: March · solver HiGHS Optimal · run 2026-09-28 19:24 UTC · 44 ms</t>
         </is>
       </c>
     </row>
@@ -798,6 +798,157 @@
       <c r="E16" t="inlineStr">
         <is>
           <t>flat</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Share of demand volume that is estimated</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Facilities with estimated demand</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>134</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Total annual cost with estimates 30% lower</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>10913439.74</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Fill rate (volume) with estimates 30% lower</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Fill rate, most vulnerable quintile with estimates 30% lower</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Hubs open with estimates 30% lower</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>5</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Total annual cost with estimates 30% higher</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>15702176.75</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fill rate (volume) with estimates 30% higher</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.9965000000000001</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Fill rate, most vulnerable quintile with estimates 30% higher</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.9921</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Hubs open with estimates 30% higher</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>count</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-4.xlsx
+++ b/docs/app/api/files/results-4.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: March · solver HiGHS Optimal · run 2026-09-28 19:24 UTC · 44 ms</t>
+          <t>Conditions: March · solver HiGHS Optimal · run 2026-09-28 19:51 UTC · 76 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-4.xlsx
+++ b/docs/app/api/files/results-4.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: March · solver HiGHS Optimal · run 2026-09-28 19:51 UTC · 76 ms</t>
+          <t>Conditions: March · solver HiGHS Optimal · run 2026-09-28 22:36 UTC · 46 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-4.xlsx
+++ b/docs/app/api/files/results-4.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: March · solver HiGHS Optimal · run 2026-09-28 22:36 UTC · 46 ms</t>
+          <t>Conditions: March · solver HiGHS Optimal · run 2026-09-28 22:48 UTC · 47 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-4.xlsx
+++ b/docs/app/api/files/results-4.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: March · solver HiGHS Optimal · run 2026-09-28 22:48 UTC · 47 ms</t>
+          <t>Conditions: March · solver HiGHS Optimal · run 2026-09-28 22:57 UTC · 50 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-4.xlsx
+++ b/docs/app/api/files/results-4.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: March · solver HiGHS Optimal · run 2026-09-28 22:57 UTC · 50 ms</t>
+          <t>Conditions: March · solver HiGHS Optimal · run 2026-09-29 09:08 UTC · 80 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-4.xlsx
+++ b/docs/app/api/files/results-4.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: March · solver HiGHS Optimal · run 2026-09-29 09:08 UTC · 80 ms</t>
+          <t>Conditions: March · solver HiGHS Optimal · run 2026-09-29 09:19 UTC · 58 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-4.xlsx
+++ b/docs/app/api/files/results-4.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: March · solver HiGHS Optimal · run 2026-09-29 09:19 UTC · 58 ms</t>
+          <t>Conditions: March · solver HiGHS Optimal · run 2026-09-29 09:28 UTC · 57 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-4.xlsx
+++ b/docs/app/api/files/results-4.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: March · solver HiGHS Optimal · run 2026-09-29 09:28 UTC · 57 ms</t>
+          <t>Conditions: March · solver HiGHS Optimal · run 2026-09-29 09:40 UTC · 67 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-4.xlsx
+++ b/docs/app/api/files/results-4.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: March · solver HiGHS Optimal · run 2026-09-29 09:40 UTC · 67 ms</t>
+          <t>Conditions: March · solver HiGHS Optimal · run 2026-09-30 15:56 UTC · 41 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-4.xlsx
+++ b/docs/app/api/files/results-4.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: March · solver HiGHS Optimal · run 2026-09-30 15:56 UTC · 41 ms</t>
+          <t>Conditions: March · solver HiGHS Optimal · run 2026-10-06 14:14 UTC · 47 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-4.xlsx
+++ b/docs/app/api/files/results-4.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: March · solver HiGHS Optimal · run 2026-10-06 14:14 UTC · 47 ms</t>
+          <t>Conditions: March · solver HiGHS Optimal · run 2026-10-06 15:06 UTC · 116 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-4.xlsx
+++ b/docs/app/api/files/results-4.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: March · solver HiGHS Optimal · run 2026-10-06 15:06 UTC · 116 ms</t>
+          <t>Conditions: March · solver HiGHS Optimal · run 2026-10-06 15:14 UTC · 128 ms</t>
         </is>
       </c>
     </row>
